--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.98425129740243</v>
+        <v>4.709940835827895</v>
       </c>
       <c r="D2" t="n">
-        <v>26.37567919446339</v>
+        <v>4.286047869100301</v>
       </c>
       <c r="E2" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F2" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.57013820098174</v>
+        <v>3.830147457659533</v>
       </c>
       <c r="D3" t="n">
-        <v>24.21133215365739</v>
+        <v>3.934341474969327</v>
       </c>
       <c r="E3" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F3" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.2597297645078</v>
+        <v>6.054706086732518</v>
       </c>
       <c r="D4" t="n">
-        <v>34.87002462020234</v>
+        <v>5.666379000782881</v>
       </c>
       <c r="E4" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F4" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.93355064868059</v>
+        <v>4.539201980410596</v>
       </c>
       <c r="D5" t="n">
-        <v>19.88124965368257</v>
+        <v>3.230703068723418</v>
       </c>
       <c r="E5" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F5" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.3515778789654</v>
+        <v>5.094631405331877</v>
       </c>
       <c r="D6" t="n">
-        <v>14.29611976317578</v>
+        <v>2.323119461516065</v>
       </c>
       <c r="E6" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F6" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.99421519378375</v>
+        <v>4.874059968989859</v>
       </c>
       <c r="D7" t="n">
-        <v>30.63138074514343</v>
+        <v>4.977599371085807</v>
       </c>
       <c r="E7" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F7" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.9012048776848</v>
+        <v>5.508945792623781</v>
       </c>
       <c r="D8" t="n">
-        <v>36.32651182952515</v>
+        <v>5.903058172297838</v>
       </c>
       <c r="E8" t="n">
-        <v>4.055222472983353</v>
+        <v>0.6589736518597947</v>
       </c>
       <c r="F8" t="n">
-        <v>7.382522932275102</v>
+        <v>1.199659976494704</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
